--- a/content/post/drafts/season-prediction/feature-selection-logistic.xlsx
+++ b/content/post/drafts/season-prediction/feature-selection-logistic.xlsx
@@ -30,25 +30,25 @@
     <t xml:space="preserve">TopThree</t>
   </si>
   <si>
-    <t xml:space="preserve">Prev_Pelo, Prev_Distance, Prev_Sprint_C, Prev_Pct_of_Max_Points</t>
+    <t xml:space="preserve">Prev_Pelo, Prev_Sprint, Prev_Sprint_F, Prev_F, Prev_Pct_of_Max_Points</t>
   </si>
   <si>
     <t xml:space="preserve">Top5</t>
   </si>
   <si>
-    <t xml:space="preserve">Prev_Distance, Prev_Sprint_C, Prev_Pct_of_Max_Points</t>
+    <t xml:space="preserve">Prev_Distance, Prev_Distance_C, Prev_C</t>
   </si>
   <si>
     <t xml:space="preserve">Top10</t>
   </si>
   <si>
-    <t xml:space="preserve">Prev_Distance_F, Prev_Sprint, Prev_Sprint_F, Prev_Pct_of_Max_Points</t>
+    <t xml:space="preserve">Prev_Distance, Prev_Sprint</t>
   </si>
   <si>
     <t xml:space="preserve">Top30</t>
   </si>
   <si>
-    <t xml:space="preserve">Prev_Distance, Prev_Sprint_F, Prev_Pct_of_Max_Points</t>
+    <t xml:space="preserve">Prev_Pelo, Prev_Distance, Prev_Pct_of_Max_Points</t>
   </si>
 </sst>
 </file>
@@ -399,10 +399,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>93.4104633782459</v>
+        <v>76.8757836980569</v>
       </c>
       <c r="D2" t="n">
-        <v>0.933282686613682</v>
+        <v>0.941860410830999</v>
       </c>
     </row>
     <row r="3">
@@ -413,10 +413,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>131.504081091794</v>
+        <v>143.256167981846</v>
       </c>
       <c r="D3" t="n">
-        <v>0.943492063492063</v>
+        <v>0.938265971316819</v>
       </c>
     </row>
     <row r="4">
@@ -427,10 +427,10 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>180.281189988604</v>
+        <v>231.677877213599</v>
       </c>
       <c r="D4" t="n">
-        <v>0.948349673202614</v>
+        <v>0.92831670956671</v>
       </c>
     </row>
     <row r="5">
@@ -441,10 +441,10 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>375.188269219191</v>
+        <v>436.238040472417</v>
       </c>
       <c r="D5" t="n">
-        <v>0.896953551912568</v>
+        <v>0.894825772088703</v>
       </c>
     </row>
   </sheetData>
@@ -471,7 +471,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>93.4104633782459</v>
+        <v>76.8757836980569</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>131.504081091794</v>
+        <v>143.256167981846</v>
       </c>
     </row>
     <row r="4">
@@ -487,7 +487,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>180.281189988604</v>
+        <v>231.677877213599</v>
       </c>
     </row>
     <row r="5">
@@ -495,7 +495,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>375.188269219191</v>
+        <v>436.238040472417</v>
       </c>
     </row>
   </sheetData>
